--- a/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0002T0006Z000C1N13_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0002T0006Z000C1N13_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>28.63556837119232</v>
+        <v>4.653279860318753</v>
       </c>
       <c r="D2" t="n">
-        <v>28.48338204413321</v>
+        <v>4.628549582171646</v>
       </c>
       <c r="E2" t="n">
-        <v>14.69183659057841</v>
+        <v>2.387423445968992</v>
       </c>
       <c r="F2" t="n">
-        <v>7.453598258444623</v>
+        <v>1.211209716997251</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>20.8416907409164</v>
+        <v>3.386774745398915</v>
       </c>
       <c r="D3" t="n">
-        <v>3.709666877604672</v>
+        <v>0.6028208676107593</v>
       </c>
       <c r="E3" t="n">
-        <v>14.69183659057841</v>
+        <v>2.387423445968992</v>
       </c>
       <c r="F3" t="n">
-        <v>7.453598258444623</v>
+        <v>1.211209716997251</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>14.75030621773623</v>
+        <v>2.396924760382137</v>
       </c>
       <c r="D4" t="n">
-        <v>14.04003776758406</v>
+        <v>2.281506137232411</v>
       </c>
       <c r="E4" t="n">
-        <v>14.69183659057841</v>
+        <v>2.387423445968992</v>
       </c>
       <c r="F4" t="n">
-        <v>7.453598258444623</v>
+        <v>1.211209716997251</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>12.76546580145809</v>
+        <v>2.074388192736939</v>
       </c>
       <c r="D5" t="n">
-        <v>11.3606449392544</v>
+        <v>1.84610480262884</v>
       </c>
       <c r="E5" t="n">
-        <v>14.69183659057841</v>
+        <v>2.387423445968992</v>
       </c>
       <c r="F5" t="n">
-        <v>7.453598258444623</v>
+        <v>1.211209716997251</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>13.50099527021565</v>
+        <v>2.193911731410043</v>
       </c>
       <c r="D6" t="n">
-        <v>16.1245154965971</v>
+        <v>2.620233768197028</v>
       </c>
       <c r="E6" t="n">
-        <v>14.69183659057841</v>
+        <v>2.387423445968992</v>
       </c>
       <c r="F6" t="n">
-        <v>7.453598258444623</v>
+        <v>1.211209716997251</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>14.98938720993722</v>
+        <v>2.435775421614799</v>
       </c>
       <c r="D7" t="n">
-        <v>1.414213562373095</v>
+        <v>0.229809703885628</v>
       </c>
       <c r="E7" t="n">
-        <v>14.69183659057841</v>
+        <v>2.387423445968992</v>
       </c>
       <c r="F7" t="n">
-        <v>7.453598258444623</v>
+        <v>1.211209716997251</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>5.961757678721181</v>
+        <v>0.9687856227921919</v>
       </c>
       <c r="D8" t="n">
-        <v>8.57240498664255</v>
+        <v>1.393015810329414</v>
       </c>
       <c r="E8" t="n">
-        <v>14.69183659057841</v>
+        <v>2.387423445968992</v>
       </c>
       <c r="F8" t="n">
-        <v>7.453598258444623</v>
+        <v>1.211209716997251</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>25.63116911847872</v>
+        <v>4.165064981752793</v>
       </c>
       <c r="D9" t="n">
-        <v>7.223355573097651</v>
+        <v>1.173795280628368</v>
       </c>
       <c r="E9" t="n">
-        <v>14.69183659057841</v>
+        <v>2.387423445968992</v>
       </c>
       <c r="F9" t="n">
-        <v>7.453598258444623</v>
+        <v>1.211209716997251</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>6.208440517066181</v>
+        <v>1.008871584023254</v>
       </c>
       <c r="D10" t="n">
-        <v>9.585616567160972</v>
+        <v>1.557662692163658</v>
       </c>
       <c r="E10" t="n">
-        <v>14.69183659057841</v>
+        <v>2.387423445968992</v>
       </c>
       <c r="F10" t="n">
-        <v>7.453598258444623</v>
+        <v>1.211209716997251</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>35.97233129285105</v>
+        <v>5.845503835088296</v>
       </c>
       <c r="D11" t="n">
-        <v>9.78365397957581</v>
+        <v>1.589843771681069</v>
       </c>
       <c r="E11" t="n">
-        <v>14.69183659057841</v>
+        <v>2.387423445968992</v>
       </c>
       <c r="F11" t="n">
-        <v>7.453598258444623</v>
+        <v>1.211209716997251</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>24.00297996549451</v>
+        <v>3.900484244392859</v>
       </c>
       <c r="D12" t="n">
-        <v>15.01381469040327</v>
+        <v>2.439744887190531</v>
       </c>
       <c r="E12" t="n">
-        <v>14.69183659057841</v>
+        <v>2.387423445968992</v>
       </c>
       <c r="F12" t="n">
-        <v>7.453598258444623</v>
+        <v>1.211209716997251</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>54.22094431737244</v>
+        <v>8.81090345157302</v>
       </c>
       <c r="D13" t="n">
-        <v>17.66165098131705</v>
+        <v>2.87001828446402</v>
       </c>
       <c r="E13" t="n">
-        <v>14.69183659057841</v>
+        <v>2.387423445968992</v>
       </c>
       <c r="F13" t="n">
-        <v>7.453598258444623</v>
+        <v>1.211209716997251</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>26.58756958757612</v>
+        <v>4.320480057981119</v>
       </c>
       <c r="D14" t="n">
-        <v>23.13954604824482</v>
+        <v>3.760176232839783</v>
       </c>
       <c r="E14" t="n">
-        <v>14.69183659057841</v>
+        <v>2.387423445968992</v>
       </c>
       <c r="F14" t="n">
-        <v>7.453598258444623</v>
+        <v>1.211209716997251</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>22.19886743361403</v>
+        <v>3.60731595796228</v>
       </c>
       <c r="D15" t="n">
-        <v>12.72792206135786</v>
+        <v>2.068287334970651</v>
       </c>
       <c r="E15" t="n">
-        <v>14.69183659057841</v>
+        <v>2.387423445968992</v>
       </c>
       <c r="F15" t="n">
-        <v>7.453598258444623</v>
+        <v>1.211209716997251</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>37.65364284577311</v>
+        <v>6.11871696243813</v>
       </c>
       <c r="D16" t="n">
-        <v>25.46350366837425</v>
+        <v>4.137819346110816</v>
       </c>
       <c r="E16" t="n">
-        <v>14.69183659057841</v>
+        <v>2.387423445968992</v>
       </c>
       <c r="F16" t="n">
-        <v>7.453598258444623</v>
+        <v>1.211209716997251</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>54.90163737683496</v>
+        <v>8.921516073735681</v>
       </c>
       <c r="D17" t="n">
-        <v>23.50531854708632</v>
+        <v>3.819614263901527</v>
       </c>
       <c r="E17" t="n">
-        <v>14.69183659057841</v>
+        <v>2.387423445968992</v>
       </c>
       <c r="F17" t="n">
-        <v>7.453598258444623</v>
+        <v>1.211209716997251</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>25.03694089209405</v>
+        <v>4.068502894965283</v>
       </c>
       <c r="D18" t="n">
-        <v>2.031608567880587</v>
+        <v>0.3301363922805954</v>
       </c>
       <c r="E18" t="n">
-        <v>14.69183659057841</v>
+        <v>2.387423445968992</v>
       </c>
       <c r="F18" t="n">
-        <v>7.453598258444623</v>
+        <v>1.211209716997251</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>30.97808277370874</v>
+        <v>5.03393845072767</v>
       </c>
       <c r="D19" t="n">
-        <v>16.44688420339853</v>
+        <v>2.67261868305226</v>
       </c>
       <c r="E19" t="n">
-        <v>14.69183659057841</v>
+        <v>2.387423445968992</v>
       </c>
       <c r="F19" t="n">
-        <v>7.453598258444623</v>
+        <v>1.211209716997251</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>15.97636569404053</v>
+        <v>2.596159425281586</v>
       </c>
       <c r="D20" t="n">
-        <v>6.708203932499369</v>
+        <v>1.090083139031148</v>
       </c>
       <c r="E20" t="n">
-        <v>14.69183659057841</v>
+        <v>2.387423445968992</v>
       </c>
       <c r="F20" t="n">
-        <v>7.453598258444623</v>
+        <v>1.211209716997251</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>58.72431678167839</v>
+        <v>9.542701477022739</v>
       </c>
       <c r="D21" t="n">
-        <v>15.57241150239744</v>
+        <v>2.530516869139583</v>
       </c>
       <c r="E21" t="n">
-        <v>14.69183659057841</v>
+        <v>2.387423445968992</v>
       </c>
       <c r="F21" t="n">
-        <v>7.453598258444623</v>
+        <v>1.211209716997251</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>54.72730609717137</v>
+        <v>8.893187240790349</v>
       </c>
       <c r="D22" t="n">
-        <v>10.97724920005007</v>
+        <v>1.783802995008137</v>
       </c>
       <c r="E22" t="n">
-        <v>14.69183659057841</v>
+        <v>2.387423445968992</v>
       </c>
       <c r="F22" t="n">
-        <v>7.453598258444623</v>
+        <v>1.211209716997251</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>30.05974160633659</v>
+        <v>4.884708011029696</v>
       </c>
       <c r="D23" t="n">
-        <v>20.84491641834053</v>
+        <v>3.387298917980336</v>
       </c>
       <c r="E23" t="n">
-        <v>14.69183659057841</v>
+        <v>2.387423445968992</v>
       </c>
       <c r="F23" t="n">
-        <v>7.453598258444623</v>
+        <v>1.211209716997251</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>35.72519102068664</v>
+        <v>5.80534354086158</v>
       </c>
       <c r="D24" t="n">
-        <v>13.04726327409476</v>
+        <v>2.120180282040399</v>
       </c>
       <c r="E24" t="n">
-        <v>14.69183659057841</v>
+        <v>2.387423445968992</v>
       </c>
       <c r="F24" t="n">
-        <v>7.453598258444623</v>
+        <v>1.211209716997251</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>15.92901998346087</v>
+        <v>2.58846574731239</v>
       </c>
       <c r="D25" t="n">
-        <v>15.69388763984269</v>
+        <v>2.550256741474438</v>
       </c>
       <c r="E25" t="n">
-        <v>14.69183659057841</v>
+        <v>2.387423445968992</v>
       </c>
       <c r="F25" t="n">
-        <v>7.453598258444623</v>
+        <v>1.211209716997251</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>17.443202073332</v>
+        <v>2.834520336916451</v>
       </c>
       <c r="D26" t="n">
-        <v>10.51189802081432</v>
+        <v>1.708183428382327</v>
       </c>
       <c r="E26" t="n">
-        <v>14.69183659057841</v>
+        <v>2.387423445968992</v>
       </c>
       <c r="F26" t="n">
-        <v>7.453598258444623</v>
+        <v>1.211209716997251</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>7.290242973172909</v>
+        <v>1.184664483140598</v>
       </c>
       <c r="D27" t="n">
-        <v>15.680531430154</v>
+        <v>2.548086357400025</v>
       </c>
       <c r="E27" t="n">
-        <v>14.69183659057841</v>
+        <v>2.387423445968992</v>
       </c>
       <c r="F27" t="n">
-        <v>7.453598258444623</v>
+        <v>1.211209716997251</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>30.43677403775651</v>
+        <v>4.945975781135433</v>
       </c>
       <c r="D28" t="n">
-        <v>5.980076520642839</v>
+        <v>0.9717624346044614</v>
       </c>
       <c r="E28" t="n">
-        <v>14.69183659057841</v>
+        <v>2.387423445968992</v>
       </c>
       <c r="F28" t="n">
-        <v>7.453598258444623</v>
+        <v>1.211209716997251</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>4.42379427685445</v>
+        <v>0.7188665699888481</v>
       </c>
       <c r="D29" t="n">
-        <v>4.442495555258778</v>
+        <v>0.7219055277295514</v>
       </c>
       <c r="E29" t="n">
-        <v>14.69183659057841</v>
+        <v>2.387423445968992</v>
       </c>
       <c r="F29" t="n">
-        <v>7.453598258444623</v>
+        <v>1.211209716997251</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>12.4343859382489</v>
+        <v>2.020587714965446</v>
       </c>
       <c r="D30" t="n">
-        <v>13.5223444869974</v>
+        <v>2.197380979137078</v>
       </c>
       <c r="E30" t="n">
-        <v>14.69183659057841</v>
+        <v>2.387423445968992</v>
       </c>
       <c r="F30" t="n">
-        <v>7.453598258444623</v>
+        <v>1.211209716997251</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>26.18700846421497</v>
+        <v>4.255388875434932</v>
       </c>
       <c r="D31" t="n">
-        <v>34.52744081107591</v>
+        <v>5.610709131799836</v>
       </c>
       <c r="E31" t="n">
-        <v>14.69183659057841</v>
+        <v>2.387423445968992</v>
       </c>
       <c r="F31" t="n">
-        <v>7.453598258444623</v>
+        <v>1.211209716997251</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>11.84811840566853</v>
+        <v>1.925319240921135</v>
       </c>
       <c r="D32" t="n">
-        <v>12.55043385421294</v>
+        <v>2.039445501309603</v>
       </c>
       <c r="E32" t="n">
-        <v>14.69183659057841</v>
+        <v>2.387423445968992</v>
       </c>
       <c r="F32" t="n">
-        <v>7.453598258444623</v>
+        <v>1.211209716997251</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1472,16 +1472,16 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>36.00732839082524</v>
+        <v>5.851190863509101</v>
       </c>
       <c r="D33" t="n">
-        <v>14.84175790726212</v>
+        <v>2.411785659930095</v>
       </c>
       <c r="E33" t="n">
-        <v>14.69183659057841</v>
+        <v>2.387423445968992</v>
       </c>
       <c r="F33" t="n">
-        <v>7.453598258444623</v>
+        <v>1.211209716997251</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
